--- a/data/trans_orig/Q4501_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q4501_R-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2007</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2007 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>101031</t>
+          <t>101035</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>142544</t>
+          <t>143443</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>272544</t>
+          <t>271736</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>332366</t>
+          <t>333704</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>388274</t>
+          <t>382741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>462087</t>
+          <t>459307</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59486</t>
+          <t>57866</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>93075</t>
+          <t>89595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>179224</t>
+          <t>182514</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>232437</t>
+          <t>235123</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252896</t>
+          <t>251671</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>315427</t>
+          <t>313599</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132999</t>
+          <t>132596</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>177363</t>
+          <t>178286</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>167641</t>
+          <t>166711</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>218907</t>
+          <t>216685</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>311183</t>
+          <t>311382</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>377957</t>
+          <t>380725</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114021</t>
+          <t>113876</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156806</t>
+          <t>157468</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102679</t>
+          <t>102281</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145210</t>
+          <t>145599</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>229730</t>
+          <t>228574</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>287439</t>
+          <t>288773</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>516778</t>
+          <t>517391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>579434</t>
+          <t>580190</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>455500</t>
+          <t>461449</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>524106</t>
+          <t>530462</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>39,88%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>990756</t>
+          <t>988286</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1082405</t>
+          <t>1082646</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,16%</t>
+          <t>46,17%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>182898</t>
+          <t>180948</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>237040</t>
+          <t>235373</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>438151</t>
+          <t>438750</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>509251</t>
+          <t>508706</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>634189</t>
+          <t>635860</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>734560</t>
+          <t>728222</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,36%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>198924</t>
+          <t>197563</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>253214</t>
+          <t>255751</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>330910</t>
+          <t>327165</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>399630</t>
+          <t>393546</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>546497</t>
+          <t>546965</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>631236</t>
+          <t>632582</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>415284</t>
+          <t>412753</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>486860</t>
+          <t>487286</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,82 +1655,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>28,81%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>402955</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>368559</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>438093</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>25,44%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>23,26%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>27,65%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>838</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>852728</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>804129</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>904144</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>26,03%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>24,55%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>28,78%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>402955</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>368234</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>438043</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>25,44%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>23,24%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>27,65%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>838</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>852728</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>801127</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>901243</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>26,03%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>24,46%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>245611</t>
+          <t>245834</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>307822</t>
+          <t>306941</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95900</t>
+          <t>93713</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137337</t>
+          <t>137117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>356109</t>
+          <t>357704</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>429652</t>
+          <t>432542</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,2%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>495414</t>
+          <t>493252</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>568668</t>
+          <t>569270</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,62%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>201960</t>
+          <t>203272</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>259848</t>
+          <t>259027</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>713746</t>
+          <t>708809</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>813473</t>
+          <t>811066</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,76%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93276</t>
+          <t>93230</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>131869</t>
+          <t>132177</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>138444</t>
+          <t>138530</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>180209</t>
+          <t>181556</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>244592</t>
+          <t>241327</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>300853</t>
+          <t>299762</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>23,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107411</t>
+          <t>108786</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>148098</t>
+          <t>148077</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99216</t>
+          <t>99407</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>136825</t>
+          <t>137033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>219355</t>
+          <t>217254</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274387</t>
+          <t>275426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,8%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>140677</t>
+          <t>140629</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>182638</t>
+          <t>183492</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>112979</t>
+          <t>112530</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>152508</t>
+          <t>150887</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>265681</t>
+          <t>262145</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>322922</t>
+          <t>322486</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,38%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51496</t>
+          <t>51973</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84481</t>
+          <t>84310</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>22446</t>
+          <t>23881</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45680</t>
+          <t>46207</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80336</t>
+          <t>81000</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>121023</t>
+          <t>120447</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67904</t>
+          <t>67411</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>102243</t>
+          <t>103372</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25644</t>
+          <t>25319</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50709</t>
+          <t>49639</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>99788</t>
+          <t>101235</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>144053</t>
+          <t>142407</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>402226</t>
+          <t>405320</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>481157</t>
+          <t>483647</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>883648</t>
+          <t>881519</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>981531</t>
+          <t>986797</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1311317</t>
+          <t>1312421</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1441957</t>
+          <t>1439413</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,65%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>393162</t>
+          <t>388636</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>471170</t>
+          <t>470156</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>639424</t>
+          <t>646839</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>737896</t>
+          <t>737946</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1058915</t>
+          <t>1050933</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1174740</t>
+          <t>1172299</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>716900</t>
+          <t>720609</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>808679</t>
+          <t>821469</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>679789</t>
+          <t>677653</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>774076</t>
+          <t>773218</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1424881</t>
+          <t>1424837</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1560381</t>
+          <t>1559160</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,47%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>440639</t>
+          <t>438416</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>521266</t>
+          <t>518153</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>241819</t>
+          <t>241102</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>306752</t>
+          <t>303398</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>699803</t>
+          <t>702190</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>803168</t>
+          <t>803980</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,09%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1107115</t>
+          <t>1103399</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1217670</t>
+          <t>1213513</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,2%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>711480</t>
+          <t>709894</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>808587</t>
+          <t>803922</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1839877</t>
+          <t>1839553</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1991501</t>
+          <t>1990532</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2012</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2012 (tasa de respuesta: 99,8%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47114</t>
+          <t>46781</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77443</t>
+          <t>76094</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>211988</t>
+          <t>211778</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>268264</t>
+          <t>269239</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>269269</t>
+          <t>264138</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>332655</t>
+          <t>329563</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34530</t>
+          <t>35400</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>62531</t>
+          <t>63606</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>118754</t>
+          <t>117776</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>164130</t>
+          <t>163597</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>163619</t>
+          <t>164093</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>221107</t>
+          <t>217432</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>112959</t>
+          <t>113805</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>158339</t>
+          <t>159778</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>254644</t>
+          <t>250970</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>314061</t>
+          <t>314535</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>379515</t>
+          <t>380590</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>456200</t>
+          <t>460760</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>111399</t>
+          <t>115030</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156883</t>
+          <t>157920</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>121318</t>
+          <t>119317</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167742</t>
+          <t>167845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>244464</t>
+          <t>244385</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>310855</t>
+          <t>308853</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>561758</t>
+          <t>561710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>626858</t>
+          <t>624200</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,38%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>498465</t>
+          <t>497226</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>571088</t>
+          <t>570487</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1079427</t>
+          <t>1077661</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1180514</t>
+          <t>1173676</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>50,85%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>205300</t>
+          <t>207107</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>267894</t>
+          <t>266571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>381032</t>
+          <t>382038</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>452777</t>
+          <t>457268</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>605855</t>
+          <t>603970</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>703426</t>
+          <t>697148</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>212198</t>
+          <t>210956</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>272961</t>
+          <t>272214</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323867</t>
+          <t>320588</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>391312</t>
+          <t>389259</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>553005</t>
+          <t>550574</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>643643</t>
+          <t>644958</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,37%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>431797</t>
+          <t>429890</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>506127</t>
+          <t>504149</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>432787</t>
+          <t>430309</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>506090</t>
+          <t>506431</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>885553</t>
+          <t>884296</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>991379</t>
+          <t>994526</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,78%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>230134</t>
+          <t>232147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>289540</t>
+          <t>292778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110178</t>
+          <t>109533</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156801</t>
+          <t>153751</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4762,12 +4762,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>352958</t>
+          <t>355761</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>427872</t>
+          <t>430011</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>713633</t>
+          <t>711354</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>803834</t>
+          <t>800152</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>352647</t>
+          <t>349915</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>422532</t>
+          <t>421196</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1086024</t>
+          <t>1090105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1201375</t>
+          <t>1205406</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,35%</t>
+          <t>32,46%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54142</t>
+          <t>54246</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84349</t>
+          <t>87066</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>121612</t>
+          <t>122414</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>163200</t>
+          <t>162185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,74%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>185741</t>
+          <t>186013</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>239131</t>
+          <t>238310</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,41%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71319</t>
+          <t>71183</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>109344</t>
+          <t>108142</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>22,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100907</t>
+          <t>100103</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>139314</t>
+          <t>142065</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>183240</t>
+          <t>185372</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>238790</t>
+          <t>239616</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,55%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>144706</t>
+          <t>142972</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>187556</t>
+          <t>187443</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>76903</t>
+          <t>78251</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>113855</t>
+          <t>112954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>228396</t>
+          <t>230937</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>288129</t>
+          <t>289985</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34476</t>
+          <t>34211</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>61526</t>
+          <t>60605</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>26311</t>
+          <t>25832</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49790</t>
+          <t>49022</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65855</t>
+          <t>66800</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105241</t>
+          <t>105645</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94501</t>
+          <t>92826</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>132472</t>
+          <t>131881</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>49433</t>
+          <t>50047</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>81534</t>
+          <t>79865</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>152377</t>
+          <t>150514</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>201563</t>
+          <t>200461</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,37%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>329260</t>
+          <t>330752</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>403640</t>
+          <t>403203</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>741100</t>
+          <t>746019</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>846968</t>
+          <t>846780</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1100942</t>
+          <t>1098842</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1228848</t>
+          <t>1223789</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>343171</t>
+          <t>340468</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>416442</t>
+          <t>417231</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>566076</t>
+          <t>569494</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>662022</t>
+          <t>663347</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>926179</t>
+          <t>932369</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1055494</t>
+          <t>1057569</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>722010</t>
+          <t>723290</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>818154</t>
+          <t>824076</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>792613</t>
+          <t>790953</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>897459</t>
+          <t>900817</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,41%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1546575</t>
+          <t>1541497</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1684236</t>
+          <t>1682803</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,18%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>398051</t>
+          <t>401393</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>481421</t>
+          <t>482320</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>277211</t>
+          <t>278166</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>347498</t>
+          <t>349393</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>695949</t>
+          <t>698870</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>802710</t>
+          <t>807040</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,6%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1403116</t>
+          <t>1395368</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1522905</t>
+          <t>1520591</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>928383</t>
+          <t>930060</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1032843</t>
+          <t>1038944</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2356729</t>
+          <t>2359722</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2517852</t>
+          <t>2531910</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,38%</t>
         </is>
       </c>
     </row>
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2016</t>
+          <t>Población según la frecuencia con la que utilizaron crema solar con el factor de protección de 15 o mayor el pasado verano al aire libre en 2016 (tasa de respuesta: 99,7%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26648</t>
+          <t>26182</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50067</t>
+          <t>49940</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>109777</t>
+          <t>113796</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153437</t>
+          <t>155835</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>143297</t>
+          <t>144148</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>194058</t>
+          <t>195414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71295</t>
+          <t>71708</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105530</t>
+          <t>108007</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>177471</t>
+          <t>178262</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>230083</t>
+          <t>229603</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257932</t>
+          <t>257046</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>321664</t>
+          <t>322258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>18,47%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>82397</t>
+          <t>83967</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>119223</t>
+          <t>119813</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>149634</t>
+          <t>146546</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>198170</t>
+          <t>197364</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>242997</t>
+          <t>244748</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>304547</t>
+          <t>304057</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68627</t>
+          <t>66037</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>102999</t>
+          <t>100518</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47708</t>
+          <t>49076</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79491</t>
+          <t>79467</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,7 +7039,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122232</t>
+          <t>122577</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168354</t>
+          <t>171099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,81%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>418498</t>
+          <t>417704</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>470375</t>
+          <t>470273</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,52%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>389521</t>
+          <t>390835</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>456614</t>
+          <t>454338</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>827201</t>
+          <t>825622</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>912555</t>
+          <t>907602</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,31%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>186670</t>
+          <t>185271</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>243163</t>
+          <t>241229</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>325927</t>
+          <t>327011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>392279</t>
+          <t>400659</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>527199</t>
+          <t>527998</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>620117</t>
+          <t>622001</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>440094</t>
+          <t>446165</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>523213</t>
+          <t>520000</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>611779</t>
+          <t>609196</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>695006</t>
+          <t>695301</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1076538</t>
+          <t>1075947</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1187064</t>
+          <t>1193711</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,48%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>493920</t>
+          <t>494123</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>572134</t>
+          <t>576593</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>412510</t>
+          <t>416388</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>491606</t>
+          <t>490586</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>929023</t>
+          <t>932377</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1043095</t>
+          <t>1038870</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,65%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139111</t>
+          <t>134402</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187582</t>
+          <t>189146</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96390</t>
+          <t>93947</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>138770</t>
+          <t>136472</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>242588</t>
+          <t>246929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>305861</t>
+          <t>309294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>637504</t>
+          <t>637166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>723206</t>
+          <t>726349</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>369182</t>
+          <t>372489</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>441167</t>
+          <t>447779</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1027347</t>
+          <t>1031214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1149864</t>
+          <t>1151269</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>79400</t>
+          <t>78012</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>117472</t>
+          <t>117897</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,82 +8029,82 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
+          <t>21,63%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>137883</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>116258</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>158741</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>25,11%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>21,17%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>28,91%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>235849</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>209669</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>264035</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>21,56%</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>137883</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>117593</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>158936</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>25,11%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>21,41%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>28,94%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>235849</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>208829</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>264278</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>21,56%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,13%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>147634</t>
+          <t>148425</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>191180</t>
+          <t>192692</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>146066</t>
+          <t>144870</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>189466</t>
+          <t>187571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>307079</t>
+          <t>306789</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>367119</t>
+          <t>365094</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,37%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>101460</t>
+          <t>102923</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>143115</t>
+          <t>144589</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>89427</t>
+          <t>93089</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>130291</t>
+          <t>129973</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>205305</t>
+          <t>204266</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>258577</t>
+          <t>263237</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23703</t>
+          <t>23579</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47335</t>
+          <t>49719</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18277</t>
+          <t>17898</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>38435</t>
+          <t>37491</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>44984</t>
+          <t>46309</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>76031</t>
+          <t>78046</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>102168</t>
+          <t>101608</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>143789</t>
+          <t>142899</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89423</t>
+          <t>88843</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>127254</t>
+          <t>128342</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>204652</t>
+          <t>205217</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>258119</t>
+          <t>261474</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>310140</t>
+          <t>306800</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>383831</t>
+          <t>380673</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>588055</t>
+          <t>585086</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>679835</t>
+          <t>677468</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>913627</t>
+          <t>913852</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1035187</t>
+          <t>1033420</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>690566</t>
+          <t>691251</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>789953</t>
+          <t>786869</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,39%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>965243</t>
+          <t>963887</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1074516</t>
+          <t>1077829</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,49%</t>
+          <t>30,59%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1687123</t>
+          <t>1683075</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1831101</t>
+          <t>1837224</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,67%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>707150</t>
+          <t>708115</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>807363</t>
+          <t>805173</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>685897</t>
+          <t>679588</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>786496</t>
+          <t>777587</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1425575</t>
+          <t>1426674</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1559405</t>
+          <t>1558851</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,63%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>246474</t>
+          <t>245148</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>310619</t>
+          <t>311190</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>176485</t>
+          <t>174126</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>233393</t>
+          <t>232507</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>436758</t>
+          <t>440367</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>524559</t>
+          <t>528432</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1187798</t>
+          <t>1192524</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1302890</t>
+          <t>1304841</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>38,78%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>879492</t>
+          <t>882962</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>991239</t>
+          <t>989904</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2107064</t>
+          <t>2106829</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2268839</t>
+          <t>2265334</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,89%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q4501_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Q4501_R-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>101035</t>
+          <t>100629</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>143443</t>
+          <t>143448</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>271736</t>
+          <t>271363</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>333704</t>
+          <t>333479</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>25,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>382741</t>
+          <t>386268</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>459307</t>
+          <t>460878</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57866</t>
+          <t>59965</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89595</t>
+          <t>91533</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>182514</t>
+          <t>181960</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>235123</t>
+          <t>235202</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251671</t>
+          <t>251189</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>313599</t>
+          <t>317574</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>132596</t>
+          <t>132628</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>178286</t>
+          <t>177251</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>166711</t>
+          <t>169171</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>216685</t>
+          <t>220522</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>311382</t>
+          <t>314429</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>380725</t>
+          <t>382752</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>113876</t>
+          <t>114288</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157468</t>
+          <t>156827</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102281</t>
+          <t>103111</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145599</t>
+          <t>146267</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>228574</t>
+          <t>227230</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>288773</t>
+          <t>288853</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,32%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>517391</t>
+          <t>518072</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>580190</t>
+          <t>578789</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>50,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,15%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1219,12 +1219,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>461449</t>
+          <t>454990</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>530462</t>
+          <t>523244</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>39,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>988286</t>
+          <t>985846</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1082646</t>
+          <t>1085983</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>46,31%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>180948</t>
+          <t>180452</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>235373</t>
+          <t>238196</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>438750</t>
+          <t>437483</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>508706</t>
+          <t>508394</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>635860</t>
+          <t>635045</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>728222</t>
+          <t>730226</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,29%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>197563</t>
+          <t>197617</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>255751</t>
+          <t>255245</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327165</t>
+          <t>334174</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>393546</t>
+          <t>397952</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>546965</t>
+          <t>548887</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632582</t>
+          <t>635672</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,31%</t>
+          <t>19,41%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>412753</t>
+          <t>413910</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>487286</t>
+          <t>487934</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>368559</t>
+          <t>368024</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>438093</t>
+          <t>439969</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>804129</t>
+          <t>804243</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>904144</t>
+          <t>900937</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>245834</t>
+          <t>246567</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>306941</t>
+          <t>308179</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93713</t>
+          <t>95213</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>137117</t>
+          <t>136033</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>357704</t>
+          <t>355345</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>432542</t>
+          <t>428764</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,09%</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>493252</t>
+          <t>493022</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>569270</t>
+          <t>571044</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>203272</t>
+          <t>200596</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>259027</t>
+          <t>259449</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,66%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>708809</t>
+          <t>717750</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>811066</t>
+          <t>809299</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,71%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93230</t>
+          <t>92630</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>132177</t>
+          <t>132195</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>138530</t>
+          <t>138786</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>181556</t>
+          <t>178684</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>241327</t>
+          <t>245988</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>299762</t>
+          <t>302240</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,41%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108786</t>
+          <t>109514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>148077</t>
+          <t>151460</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>99407</t>
+          <t>97736</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>137033</t>
+          <t>136490</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>217254</t>
+          <t>216834</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>275426</t>
+          <t>273835</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>140629</t>
+          <t>139329</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>183492</t>
+          <t>181377</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>112530</t>
+          <t>113522</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>150887</t>
+          <t>152311</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,62%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>262145</t>
+          <t>262851</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>322486</t>
+          <t>320078</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,14%</t>
         </is>
       </c>
     </row>
@@ -2435,12 +2435,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>51973</t>
+          <t>50530</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>84310</t>
+          <t>84541</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2450,12 +2450,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23881</t>
+          <t>22433</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46207</t>
+          <t>43778</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81000</t>
+          <t>79779</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>120447</t>
+          <t>119920</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,67%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>67411</t>
+          <t>68803</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>103372</t>
+          <t>104697</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25319</t>
+          <t>26691</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49639</t>
+          <t>49118</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>101235</t>
+          <t>100501</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>142407</t>
+          <t>141594</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,78%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>405320</t>
+          <t>403778</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>483647</t>
+          <t>483688</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>881519</t>
+          <t>882901</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>986797</t>
+          <t>987585</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1312421</t>
+          <t>1308222</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1439413</t>
+          <t>1442146</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>388636</t>
+          <t>390318</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>470156</t>
+          <t>465146</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>646839</t>
+          <t>643551</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>737946</t>
+          <t>735123</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1050933</t>
+          <t>1053344</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1172299</t>
+          <t>1173248</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>720609</t>
+          <t>714891</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>821469</t>
+          <t>810884</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>677653</t>
+          <t>675193</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>773218</t>
+          <t>772620</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1424837</t>
+          <t>1425428</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1559160</t>
+          <t>1559737</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,46%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>438416</t>
+          <t>438473</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>518153</t>
+          <t>518267</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>241102</t>
+          <t>240472</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>303398</t>
+          <t>304992</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>702190</t>
+          <t>695857</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>803980</t>
+          <t>801297</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,05%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1103399</t>
+          <t>1107958</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1213513</t>
+          <t>1218354</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>709894</t>
+          <t>711978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>803922</t>
+          <t>806871</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1839553</t>
+          <t>1839698</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1990532</t>
+          <t>1995825</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,02%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46781</t>
+          <t>46880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76094</t>
+          <t>76262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>211778</t>
+          <t>211676</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>269239</t>
+          <t>268596</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>264138</t>
+          <t>269763</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>329563</t>
+          <t>331252</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,35%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>35400</t>
+          <t>35141</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63606</t>
+          <t>63600</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>117776</t>
+          <t>117657</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>163597</t>
+          <t>164041</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>164093</t>
+          <t>162454</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217432</t>
+          <t>219914</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>113805</t>
+          <t>115220</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>159778</t>
+          <t>159767</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>250970</t>
+          <t>252948</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>314535</t>
+          <t>313754</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>380590</t>
+          <t>380690</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>460760</t>
+          <t>453638</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>115030</t>
+          <t>112384</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157920</t>
+          <t>158811</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>119317</t>
+          <t>121235</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>167845</t>
+          <t>169234</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>244385</t>
+          <t>248248</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>308853</t>
+          <t>310616</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>561710</t>
+          <t>562157</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>624200</t>
+          <t>624491</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>497226</t>
+          <t>494411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>570487</t>
+          <t>571983</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,26%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>42,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1077661</t>
+          <t>1073570</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1173676</t>
+          <t>1178621</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>207107</t>
+          <t>210712</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>266571</t>
+          <t>270644</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>382038</t>
+          <t>380494</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>457268</t>
+          <t>452270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>603970</t>
+          <t>605745</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>697148</t>
+          <t>700113</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,85%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>210956</t>
+          <t>212321</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>272214</t>
+          <t>271056</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>320588</t>
+          <t>318266</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>389259</t>
+          <t>387177</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>550574</t>
+          <t>547921</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>644958</t>
+          <t>640807</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>429890</t>
+          <t>428707</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>504149</t>
+          <t>510860</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>430309</t>
+          <t>432191</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>506431</t>
+          <t>509525</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>884296</t>
+          <t>886584</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>994526</t>
+          <t>990830</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>232147</t>
+          <t>230478</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>292778</t>
+          <t>292278</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4727,12 +4727,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109533</t>
+          <t>109626</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>153751</t>
+          <t>156521</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>355761</t>
+          <t>355706</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>430011</t>
+          <t>429704</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,57%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>711354</t>
+          <t>709768</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>800152</t>
+          <t>798127</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>349915</t>
+          <t>351928</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>421196</t>
+          <t>422191</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1090105</t>
+          <t>1083244</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1205406</t>
+          <t>1194678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,17%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54246</t>
+          <t>54265</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87066</t>
+          <t>86518</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>122414</t>
+          <t>123288</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>162185</t>
+          <t>164561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>186013</t>
+          <t>184848</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>238310</t>
+          <t>240296</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71183</t>
+          <t>72269</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>108142</t>
+          <t>108130</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,7 +5183,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>100103</t>
+          <t>99787</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142065</t>
+          <t>141263</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>185372</t>
+          <t>179324</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>239616</t>
+          <t>236181</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,18%</t>
         </is>
       </c>
     </row>
@@ -5281,12 +5281,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>142972</t>
+          <t>143880</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>187443</t>
+          <t>186248</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5296,12 +5296,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>78251</t>
+          <t>77100</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>112954</t>
+          <t>114455</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>230937</t>
+          <t>229134</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>289985</t>
+          <t>286437</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -5394,12 +5394,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34211</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60605</t>
+          <t>63107</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5429,12 +5429,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25832</t>
+          <t>25804</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>49022</t>
+          <t>51787</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5444,12 +5444,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>66800</t>
+          <t>64914</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105645</t>
+          <t>102047</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>92826</t>
+          <t>95185</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>131881</t>
+          <t>133486</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5522,12 +5522,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5542,12 +5542,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>50047</t>
+          <t>49682</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>79865</t>
+          <t>80583</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>150514</t>
+          <t>152676</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>200461</t>
+          <t>203802</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,73%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>330752</t>
+          <t>332932</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>403203</t>
+          <t>405446</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>746019</t>
+          <t>743771</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>846780</t>
+          <t>852041</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1098842</t>
+          <t>1096589</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1223789</t>
+          <t>1228623</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,65%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>340468</t>
+          <t>343437</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>417231</t>
+          <t>420890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>569494</t>
+          <t>561957</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>663347</t>
+          <t>660680</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>932369</t>
+          <t>931865</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1057569</t>
+          <t>1054191</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>723290</t>
+          <t>718847</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>824076</t>
+          <t>818307</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>790953</t>
+          <t>792485</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>900817</t>
+          <t>901308</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1541497</t>
+          <t>1543782</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1682803</t>
+          <t>1691298</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>24,3%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>401393</t>
+          <t>399937</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>482320</t>
+          <t>482373</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>278166</t>
+          <t>273615</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>349393</t>
+          <t>342722</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,86%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>698870</t>
+          <t>700930</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>807040</t>
+          <t>810147</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1395368</t>
+          <t>1401231</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1520591</t>
+          <t>1518645</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6204,12 +6204,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>930060</t>
+          <t>924443</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1038944</t>
+          <t>1041018</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2359722</t>
+          <t>2360556</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2531910</t>
+          <t>2522992</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,25%</t>
         </is>
       </c>
     </row>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26182</t>
+          <t>26664</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>49940</t>
+          <t>49115</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113796</t>
+          <t>110510</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155835</t>
+          <t>155754</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>144148</t>
+          <t>145627</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>195414</t>
+          <t>196364</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,26%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71708</t>
+          <t>69908</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>108007</t>
+          <t>104069</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>13,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>178262</t>
+          <t>175893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>229603</t>
+          <t>229324</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257046</t>
+          <t>260447</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>322258</t>
+          <t>321960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,46%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>83967</t>
+          <t>83298</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>119813</t>
+          <t>119196</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>146546</t>
+          <t>146862</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>197364</t>
+          <t>199876</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>244748</t>
+          <t>241690</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>304057</t>
+          <t>303388</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,39%</t>
         </is>
       </c>
     </row>
@@ -6989,12 +6989,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66037</t>
+          <t>67003</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100518</t>
+          <t>102903</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7024,12 +7024,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49076</t>
+          <t>47054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79467</t>
+          <t>79149</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122577</t>
+          <t>123795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>171099</t>
+          <t>169629</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7074,12 +7074,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>417704</t>
+          <t>419172</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>470273</t>
+          <t>472804</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>390835</t>
+          <t>388461</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>454338</t>
+          <t>457696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>825622</t>
+          <t>819862</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>907602</t>
+          <t>908187</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,06%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>185271</t>
+          <t>180629</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>241229</t>
+          <t>239065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>327011</t>
+          <t>325403</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>400659</t>
+          <t>394240</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>527998</t>
+          <t>526364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>622001</t>
+          <t>617128</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>446165</t>
+          <t>443642</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520000</t>
+          <t>524301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>609196</t>
+          <t>611242</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>695301</t>
+          <t>696394</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1075947</t>
+          <t>1073557</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1193711</t>
+          <t>1191682</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>29,43%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>494123</t>
+          <t>497857</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>576593</t>
+          <t>579740</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>416388</t>
+          <t>415874</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>490586</t>
+          <t>490670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>932377</t>
+          <t>930015</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1038870</t>
+          <t>1037575</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -7671,12 +7671,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134402</t>
+          <t>137887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189146</t>
+          <t>185683</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7686,12 +7686,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93947</t>
+          <t>96148</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136472</t>
+          <t>139478</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>246929</t>
+          <t>242435</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>309294</t>
+          <t>309818</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
     </row>
@@ -7784,12 +7784,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>637166</t>
+          <t>635260</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>726349</t>
+          <t>725042</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7799,12 +7799,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,14%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>372489</t>
+          <t>362926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>447779</t>
+          <t>441413</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1031214</t>
+          <t>1026530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1151269</t>
+          <t>1148930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,37%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>78012</t>
+          <t>81403</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>117897</t>
+          <t>117340</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>116258</t>
+          <t>117902</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>158741</t>
+          <t>160396</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>209669</t>
+          <t>206024</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>264035</t>
+          <t>262191</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>23,96%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>148425</t>
+          <t>147724</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>192692</t>
+          <t>192777</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144870</t>
+          <t>147430</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>187571</t>
+          <t>191330</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>306789</t>
+          <t>304002</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>365094</t>
+          <t>369164</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,04%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,74%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>102923</t>
+          <t>102321</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>144589</t>
+          <t>143194</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,82 +8255,82 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>18,78%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>26,28%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>109821</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>89927</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>128803</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>20,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>16,38%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>23,46%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>231236</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>206629</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>259437</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>21,14%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
           <t>18,89%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>26,53%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>109821</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>93089</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>129973</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>20,0%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>23,67%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>231236</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>204266</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>263237</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>21,14%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>18,67%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,71%</t>
         </is>
       </c>
     </row>
@@ -8353,12 +8353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23579</t>
+          <t>23746</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>49719</t>
+          <t>47250</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8368,12 +8368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8388,12 +8388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17898</t>
+          <t>17863</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37491</t>
+          <t>39861</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8403,12 +8403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46309</t>
+          <t>46592</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>78046</t>
+          <t>79306</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8438,12 +8438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,25%</t>
         </is>
       </c>
     </row>
@@ -8466,12 +8466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>101608</t>
+          <t>104163</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>142899</t>
+          <t>143887</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>19,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8501,12 +8501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>88843</t>
+          <t>88623</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128342</t>
+          <t>127615</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8516,12 +8516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>205217</t>
+          <t>202911</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>261474</t>
+          <t>263221</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>306800</t>
+          <t>308602</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>380673</t>
+          <t>381960</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>585086</t>
+          <t>586873</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>677468</t>
+          <t>682716</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>913852</t>
+          <t>917839</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1033420</t>
+          <t>1031735</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>691251</t>
+          <t>693942</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>786869</t>
+          <t>785983</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>963887</t>
+          <t>970958</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1077829</t>
+          <t>1079792</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1683075</t>
+          <t>1691322</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1837224</t>
+          <t>1829557</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,56%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>708115</t>
+          <t>709583</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>805173</t>
+          <t>808155</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>679588</t>
+          <t>684183</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>777587</t>
+          <t>782956</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1426674</t>
+          <t>1418441</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1558851</t>
+          <t>1555364</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -9035,12 +9035,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>245148</t>
+          <t>242921</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>311190</t>
+          <t>306219</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9050,12 +9050,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>174126</t>
+          <t>175919</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>232507</t>
+          <t>232276</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>440367</t>
+          <t>437422</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>528432</t>
+          <t>526440</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -9148,12 +9148,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1192524</t>
+          <t>1192890</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1304841</t>
+          <t>1306587</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>38,78%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>882962</t>
+          <t>883535</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>989904</t>
+          <t>993024</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2106829</t>
+          <t>2100584</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2265334</t>
+          <t>2259730</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,81%</t>
         </is>
       </c>
     </row>
